--- a/docs/sample-output/05-medical-office/proforma.xlsx
+++ b/docs/sample-output/05-medical-office/proforma.xlsx
@@ -264,7 +264,7 @@
     <t>Leverage Impact</t>
   </si>
   <si>
-    <t>Optimal holding period: Year 5 at -27.42% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
+    <t>Optimal holding period: Year 5 at -27.27% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
   </si>
   <si>
     <t>Acquisition-Price Sensitivity   ·   Desert Ridge MOB · 5-Year Before-Tax</t>
@@ -1077,7 +1077,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="6">
-        <v>33869764.37</v>
+        <v>33836121.87</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1085,7 +1085,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="7">
-        <v>0.04181322268820969</v>
+        <v>0.0418547966413268</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1093,7 +1093,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="6">
-        <v>12074570.997904997</v>
+        <v>12062577.446654994</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1109,7 +1109,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>-0.2741712219369265</v>
+        <v>-0.2726929554963271</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1117,7 +1117,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="8">
-        <v>0.14643941234961408</v>
+        <v>0.14896119753354956</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1133,7 +1133,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="7">
-        <v>-0.2741712219369265</v>
+        <v>-0.2726929554963271</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1148,7 +1148,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="6">
-        <v>33869764.37</v>
+        <v>33836121.87</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1164,7 +1164,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="6">
-        <v>220153.46840500002</v>
+        <v>219934.792155</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1172,7 +1172,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="6">
-        <v>33869764.37</v>
+        <v>33836121.87</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1180,7 +1180,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="6">
-        <v>-22015346.8405</v>
+        <v>-21993479.2155</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1188,7 +1188,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="10">
-        <v>12074570.997904997</v>
+        <v>12062577.446654994</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1196,7 +1196,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="11">
-        <v>20.907261956790123</v>
+        <v>20.88649498148148</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1204,7 +1204,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="12">
-        <v>752.6614304444444</v>
+        <v>751.9138193333333</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1219,7 +1219,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="6">
-        <v>22015346.8405</v>
+        <v>21993479.2155</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1251,7 +1251,7 @@
         <v>42</v>
       </c>
       <c r="B35" s="12">
-        <v>148649.19846257777</v>
+        <v>148501.54669256113</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1259,7 +1259,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="6">
-        <v>1783790.3815509332</v>
+        <v>1782018.5603107335</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1494,19 +1494,19 @@
         <v>60</v>
       </c>
       <c r="B13" s="16">
-        <v>-1783790.3815509332</v>
+        <v>-1782018.5603107335</v>
       </c>
       <c r="C13" s="16">
-        <v>-1783790.3815509332</v>
+        <v>-1782018.5603107335</v>
       </c>
       <c r="D13" s="16">
-        <v>-1783790.3815509332</v>
+        <v>-1782018.5603107335</v>
       </c>
       <c r="E13" s="16">
-        <v>-1783790.3815509332</v>
+        <v>-1782018.5603107335</v>
       </c>
       <c r="F13" s="16">
-        <v>-1783790.3815509332</v>
+        <v>-1782018.5603107335</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1514,19 +1514,19 @@
         <v>61</v>
       </c>
       <c r="B14" s="18">
-        <v>-367586.38155093323</v>
+        <v>-365814.5603107335</v>
       </c>
       <c r="C14" s="18">
-        <v>-325100.2615509331</v>
+        <v>-323328.4403107334</v>
       </c>
       <c r="D14" s="18">
-        <v>-281339.55795093323</v>
+        <v>-279567.7367107335</v>
       </c>
       <c r="E14" s="18">
-        <v>-236266.03324293322</v>
+        <v>-234494.2120027335</v>
       </c>
       <c r="F14" s="18">
-        <v>-189840.30279369303</v>
+        <v>-188068.4815534933</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1670,19 +1670,19 @@
         <v>68</v>
       </c>
       <c r="B9" s="16">
-        <v>-21651851.61493602</v>
+        <v>-21630345.04612739</v>
       </c>
       <c r="C9" s="16">
-        <v>-21264012.44092194</v>
+        <v>-21242891.108906493</v>
       </c>
       <c r="D9" s="16">
-        <v>-20850198.959145</v>
+        <v>-20829488.663944233</v>
       </c>
       <c r="E9" s="16">
-        <v>-20408671.622109834</v>
+        <v>-20388399.891620472</v>
       </c>
       <c r="F9" s="16">
-        <v>-19937574.381603673</v>
+        <v>-19917770.58731666</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1690,19 +1690,19 @@
         <v>69</v>
       </c>
       <c r="B10" s="18">
-        <v>-1122351.6149360202</v>
+        <v>-1100845.0461273901</v>
       </c>
       <c r="C10" s="18">
-        <v>-117962.44092193991</v>
+        <v>-96841.10890649259</v>
       </c>
       <c r="D10" s="18">
-        <v>929501.0408550017</v>
+        <v>950211.3360557668</v>
       </c>
       <c r="E10" s="18">
-        <v>2024628.377890166</v>
+        <v>2044900.108379528</v>
       </c>
       <c r="F10" s="18">
-        <v>3168325.618396327</v>
+        <v>3188129.4126833417</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1740,19 +1740,19 @@
         <v>71</v>
       </c>
       <c r="B13" s="21">
-        <v>1.0019366781552994</v>
+        <v>1.000941464420518</v>
       </c>
       <c r="C13" s="21">
-        <v>0.9552995391042697</v>
+        <v>0.9543506495757443</v>
       </c>
       <c r="D13" s="21">
-        <v>0.9094564668561894</v>
+        <v>0.9085531127952645</v>
       </c>
       <c r="E13" s="21">
-        <v>0.8642615237617445</v>
+        <v>0.8634030613881796</v>
       </c>
       <c r="F13" s="21">
-        <v>0.8197341658417759</v>
+        <v>0.8189199320498585</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1760,19 +1760,19 @@
         <v>72</v>
       </c>
       <c r="B14" s="22">
-        <v>0.7939296089087935</v>
+        <v>0.794718995380752</v>
       </c>
       <c r="C14" s="22">
-        <v>0.8177474971760574</v>
+        <v>0.8185605652421746</v>
       </c>
       <c r="D14" s="22">
-        <v>0.8422799220913391</v>
+        <v>0.8431173821994397</v>
       </c>
       <c r="E14" s="22">
-        <v>0.8675483197540792</v>
+        <v>0.868410903665423</v>
       </c>
       <c r="F14" s="22">
-        <v>0.8935747693467017</v>
+        <v>0.8944632307753857</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1780,19 +1780,19 @@
         <v>73</v>
       </c>
       <c r="B15" s="21">
-        <v>0.06432803490493798</v>
+        <v>0.06439199483281044</v>
       </c>
       <c r="C15" s="21">
-        <v>0.06625787595208611</v>
+        <v>0.06632375467779476</v>
       </c>
       <c r="D15" s="21">
-        <v>0.06824561223064869</v>
+        <v>0.0683134673181286</v>
       </c>
       <c r="E15" s="21">
-        <v>0.07029298059756815</v>
+        <v>0.07036287133767247</v>
       </c>
       <c r="F15" s="21">
-        <v>0.0724017700154952</v>
+        <v>0.07247375747780264</v>
       </c>
     </row>
   </sheetData>
@@ -1868,19 +1868,19 @@
         <v>75</v>
       </c>
       <c r="B5" s="21">
-        <v>-0.030443017943636377</v>
+        <v>-0.030326400964345766</v>
       </c>
       <c r="C5" s="21">
-        <v>-0.026924373678148875</v>
+        <v>-0.026804258189479544</v>
       </c>
       <c r="D5" s="21">
-        <v>-0.02330017008469677</v>
+        <v>-0.02317645113136736</v>
       </c>
       <c r="E5" s="21">
-        <v>-0.019567240383441088</v>
+        <v>-0.01943980986151179</v>
       </c>
       <c r="F5" s="21">
-        <v>-0.01572232279114772</v>
+        <v>-0.015591069353560546</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1888,19 +1888,19 @@
         <v>76</v>
       </c>
       <c r="B6" s="21">
-        <v>0.3275144586234569</v>
+        <v>0.33230340782076</v>
       </c>
       <c r="C6" s="21">
-        <v>2.7559641781748474</v>
+        <v>3.3387519407995567</v>
       </c>
       <c r="D6" s="21">
-        <v>-0.30267804508550417</v>
+        <v>-0.294216377033757</v>
       </c>
       <c r="E6" s="21">
-        <v>-0.11669600002798658</v>
+        <v>-0.11467269772339021</v>
       </c>
       <c r="F6" s="21">
-        <v>-0.059918179397792516</v>
+        <v>-0.058990228190016404</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1908,19 +1908,19 @@
         <v>77</v>
       </c>
       <c r="B7" s="23">
-        <v>-0.12339469425004546</v>
+        <v>-0.12158758050874399</v>
       </c>
       <c r="C7" s="23">
-        <v>-0.06713688495967751</v>
+        <v>-0.06515888606758055</v>
       </c>
       <c r="D7" s="23">
-        <v>-0.0036875148777975866</v>
+        <v>-0.0015336192748394394</v>
       </c>
       <c r="E7" s="23">
-        <v>0.067442242356745</v>
+        <v>0.06977738901713744</v>
       </c>
       <c r="F7" s="23">
-        <v>0.14643941234961408</v>
+        <v>0.14896119753354956</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1928,19 +1928,19 @@
         <v>78</v>
       </c>
       <c r="B8" s="21">
-        <v>-0.35205619501052504</v>
+        <v>-0.3514119589620124</v>
       </c>
       <c r="C8" s="21">
-        <v>-0.16187931659859883</v>
+        <v>-0.16145209568453384</v>
       </c>
       <c r="D8" s="21">
-        <v>-0.08677805243826621</v>
+        <v>-0.08646031253101706</v>
       </c>
       <c r="E8" s="21">
-        <v>-0.046762233881772496</v>
+        <v>-0.04650770517805341</v>
       </c>
       <c r="F8" s="21">
-        <v>-0.02195675869129972</v>
+        <v>-0.02174307179714887</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1970,13 +1970,13 @@
       <c r="B10" s="24"/>
       <c r="C10" s="24"/>
       <c r="D10" s="24">
-        <v>-0.6557326052418322</v>
+        <v>-0.6509032145003515</v>
       </c>
       <c r="E10" s="24">
-        <v>-0.4126986430361734</v>
+        <v>-0.41035513389800005</v>
       </c>
       <c r="F10" s="24">
-        <v>-0.2741712219369265</v>
+        <v>-0.2726929554963271</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1986,13 +1986,13 @@
       <c r="B11" s="25"/>
       <c r="C11" s="25"/>
       <c r="D11" s="21">
-        <v>-0.5689</v>
+        <v>-0.5644</v>
       </c>
       <c r="E11" s="21">
-        <v>-0.3659</v>
+        <v>-0.3639</v>
       </c>
       <c r="F11" s="21">
-        <v>-0.2522</v>
+        <v>-0.251</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2086,19 +2086,19 @@
         <v>18</v>
       </c>
       <c r="B6" s="18">
-        <v>30482788</v>
+        <v>30452510</v>
       </c>
       <c r="C6" s="18">
-        <v>32176276</v>
+        <v>32144316</v>
       </c>
       <c r="D6" s="18">
-        <v>33869764</v>
+        <v>33836122</v>
       </c>
       <c r="E6" s="18">
-        <v>35563253</v>
+        <v>35527928</v>
       </c>
       <c r="F6" s="18">
-        <v>37256741</v>
+        <v>37219734</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2106,19 +2106,19 @@
         <v>19</v>
       </c>
       <c r="B7" s="21">
-        <v>0.046459136218117585</v>
+        <v>0.046505329117369966</v>
       </c>
       <c r="C7" s="21">
-        <v>0.044013918826404895</v>
+        <v>0.044057680368747</v>
       </c>
       <c r="D7" s="21">
-        <v>0.041813223144985597</v>
+        <v>0.04185479648051866</v>
       </c>
       <c r="E7" s="21">
-        <v>0.039822116385134956</v>
+        <v>0.03986171104602554</v>
       </c>
       <c r="F7" s="21">
-        <v>0.03801202042873261</v>
+        <v>0.03804981518675012</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2126,19 +2126,19 @@
         <v>90</v>
       </c>
       <c r="B8" s="16">
-        <v>19813812.2</v>
+        <v>19794131.5</v>
       </c>
       <c r="C8" s="16">
-        <v>20914579.400000002</v>
+        <v>20893805.400000002</v>
       </c>
       <c r="D8" s="16">
-        <v>22015346.6</v>
+        <v>21993479.3</v>
       </c>
       <c r="E8" s="16">
-        <v>23116114.45</v>
+        <v>23093153.2</v>
       </c>
       <c r="F8" s="16">
-        <v>24216881.650000002</v>
+        <v>24192827.1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2146,19 +2146,19 @@
         <v>20</v>
       </c>
       <c r="B9" s="16">
-        <v>10867113.922000002</v>
+        <v>10856319.815000001</v>
       </c>
       <c r="C9" s="16">
-        <v>11470842.393999998</v>
+        <v>11459448.654</v>
       </c>
       <c r="D9" s="16">
-        <v>12074570.865999997</v>
+        <v>12062577.492999997</v>
       </c>
       <c r="E9" s="16">
-        <v>12678299.694500003</v>
+        <v>12665706.331999999</v>
       </c>
       <c r="F9" s="16">
-        <v>13282028.166499998</v>
+        <v>13268835.170999996</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2166,19 +2166,19 @@
         <v>91</v>
       </c>
       <c r="B10" s="21">
-        <v>0.046459136218117585</v>
+        <v>0.046505329117369966</v>
       </c>
       <c r="C10" s="21">
-        <v>0.044013918826404895</v>
+        <v>0.044057680368747</v>
       </c>
       <c r="D10" s="21">
-        <v>0.041813223144985597</v>
+        <v>0.04185479648051866</v>
       </c>
       <c r="E10" s="21">
-        <v>0.039822116385134956</v>
+        <v>0.03986171104602554</v>
       </c>
       <c r="F10" s="21">
-        <v>0.03801202042873261</v>
+        <v>0.03804981518675012</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2186,19 +2186,19 @@
         <v>92</v>
       </c>
       <c r="B11" s="21">
-        <v>0.047852910304661114</v>
+        <v>0.04790048899089107</v>
       </c>
       <c r="C11" s="21">
-        <v>0.04533433639119704</v>
+        <v>0.04537941077980941</v>
       </c>
       <c r="D11" s="21">
-        <v>0.04306761983933517</v>
+        <v>0.04311044037493422</v>
       </c>
       <c r="E11" s="21">
-        <v>0.04101677987668901</v>
+        <v>0.041057562377406306</v>
       </c>
       <c r="F11" s="21">
-        <v>0.039152381041594596</v>
+        <v>0.03919130964235263</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2206,19 +2206,19 @@
         <v>93</v>
       </c>
       <c r="B12" s="21">
-        <v>0.04928849761380094</v>
+        <v>0.049337503660617794</v>
       </c>
       <c r="C12" s="21">
-        <v>0.04669436648293295</v>
+        <v>0.04674079310320369</v>
       </c>
       <c r="D12" s="21">
-        <v>0.044359648434515224</v>
+        <v>0.044403753586182246</v>
       </c>
       <c r="E12" s="21">
-        <v>0.042247283272989676</v>
+        <v>0.04228928924872849</v>
       </c>
       <c r="F12" s="21">
-        <v>0.04032695247284243</v>
+        <v>0.04036704893162321</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2226,19 +2226,19 @@
         <v>94</v>
       </c>
       <c r="B13" s="21">
-        <v>0.05076715254221497</v>
+        <v>0.05081762877043633</v>
       </c>
       <c r="C13" s="21">
-        <v>0.04809519747742094</v>
+        <v>0.0481430168962998</v>
       </c>
       <c r="D13" s="21">
-        <v>0.04569043788755068</v>
+        <v>0.04573586619376772</v>
       </c>
       <c r="E13" s="21">
-        <v>0.043514701771179366</v>
+        <v>0.04355796792619035</v>
       </c>
       <c r="F13" s="21">
-        <v>0.04153676104702771</v>
+        <v>0.0415780603995719</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2246,19 +2246,19 @@
         <v>95</v>
       </c>
       <c r="B14" s="21">
-        <v>0.052290167118481425</v>
+        <v>0.05234215763354943</v>
       </c>
       <c r="C14" s="21">
-        <v>0.049538053401743574</v>
+        <v>0.0495873074031888</v>
       </c>
       <c r="D14" s="21">
-        <v>0.047061151024177204</v>
+        <v>0.04710794217958075</v>
       </c>
       <c r="E14" s="21">
-        <v>0.044820142824314756</v>
+        <v>0.04486470696397606</v>
       </c>
       <c r="F14" s="21">
-        <v>0.04278286387843854</v>
+        <v>0.04282540221155907</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2266,19 +2266,19 @@
         <v>96</v>
       </c>
       <c r="B15" s="21">
-        <v>-0.017411002431973268</v>
+        <v>-0.017281429082036722</v>
       </c>
       <c r="C15" s="21">
-        <v>-0.024269957247436635</v>
+        <v>-0.024147203972984765</v>
       </c>
       <c r="D15" s="21">
-        <v>-0.03044301666235753</v>
+        <v>-0.030326401415420468</v>
       </c>
       <c r="E15" s="21">
-        <v>-0.036028168863902074</v>
+        <v>-0.035917103896467094</v>
       </c>
       <c r="F15" s="21">
-        <v>-0.04110557687625088</v>
+        <v>-0.040999560724729135</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2286,19 +2286,19 @@
         <v>97</v>
       </c>
       <c r="B16" s="21">
-        <v>-0.013501397701135875</v>
+        <v>-0.013367937150701231</v>
       </c>
       <c r="C16" s="21">
-        <v>-0.02056612116106314</v>
+        <v>-0.020439685288377717</v>
       </c>
       <c r="D16" s="21">
-        <v>-0.026924372358431665</v>
+        <v>-0.026804258654086487</v>
       </c>
       <c r="E16" s="21">
-        <v>-0.032677079126022544</v>
+        <v>-0.032562682209564514</v>
       </c>
       <c r="F16" s="21">
-        <v>-0.037906809378741815</v>
+        <v>-0.037797612742674416</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2306,19 +2306,19 @@
         <v>98</v>
       </c>
       <c r="B17" s="21">
-        <v>-0.00947450482837338</v>
+        <v>-0.009337040461425696</v>
       </c>
       <c r="C17" s="21">
-        <v>-0.016751169992098462</v>
+        <v>-0.016620941043232473</v>
       </c>
       <c r="D17" s="21">
-        <v>-0.02330016872538804</v>
+        <v>-0.02317645160991251</v>
       </c>
       <c r="E17" s="21">
-        <v>-0.02922545669600665</v>
+        <v>-0.029107627872054877</v>
       </c>
       <c r="F17" s="21">
-        <v>-0.034612078856307495</v>
+        <v>-0.034499606321158074</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2326,19 +2326,19 @@
         <v>99</v>
       </c>
       <c r="B18" s="21">
-        <v>-0.005326805169427999</v>
+        <v>-0.005185216871471884</v>
       </c>
       <c r="C18" s="21">
-        <v>-0.012821770288064832</v>
+        <v>-0.012687634470732862</v>
       </c>
       <c r="D18" s="21">
-        <v>-0.019567238983353098</v>
+        <v>-0.0194398103544133</v>
       </c>
       <c r="E18" s="21">
-        <v>-0.025670285593090265</v>
+        <v>-0.02554892190441994</v>
       </c>
       <c r="F18" s="21">
-        <v>-0.031218506418200138</v>
+        <v>-0.03110265970699623</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2346,19 +2346,19 @@
         <v>100</v>
       </c>
       <c r="B19" s="21">
-        <v>-0.00105467452071424</v>
+        <v>-0.0009088385738194408</v>
       </c>
       <c r="C19" s="21">
-        <v>-0.008774488592910178</v>
+        <v>-0.008636328701058248</v>
       </c>
       <c r="D19" s="21">
-        <v>-0.01572232134905709</v>
+        <v>-0.0155910698612491</v>
       </c>
       <c r="E19" s="21">
-        <v>-0.02200845935708638</v>
+        <v>-0.02188345475775594</v>
       </c>
       <c r="F19" s="21">
-        <v>-0.027723126806949546</v>
+        <v>-0.027603804694409522</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2366,19 +2366,19 @@
         <v>101</v>
       </c>
       <c r="B20" s="21">
-        <v>-0.28006244048270645</v>
+        <v>-0.27934662857064774</v>
       </c>
       <c r="C20" s="21">
-        <v>-0.3179538862730165</v>
+        <v>-0.3172757510219527</v>
       </c>
       <c r="D20" s="21">
-        <v>-0.3520561879316689</v>
+        <v>-0.3514119614530872</v>
       </c>
       <c r="E20" s="21">
-        <v>-0.3829106690546008</v>
+        <v>-0.38229710440758335</v>
       </c>
       <c r="F20" s="21">
-        <v>-0.41096018033347403</v>
+        <v>-0.4103745072437186</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2386,19 +2386,19 @@
         <v>102</v>
       </c>
       <c r="B21" s="21">
-        <v>-0.115319844377791</v>
+        <v>-0.11486828577023114</v>
       </c>
       <c r="C21" s="21">
-        <v>-0.1395346511588526</v>
+        <v>-0.13909576132285012</v>
       </c>
       <c r="D21" s="21">
-        <v>-0.16187931190348764</v>
+        <v>-0.16145209733732382</v>
       </c>
       <c r="E21" s="21">
-        <v>-0.18258210159276145</v>
+        <v>-0.18216567968269431</v>
       </c>
       <c r="F21" s="21">
-        <v>-0.20183412698448472</v>
+        <v>-0.20142774200768576</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2406,19 +2406,19 @@
         <v>103</v>
       </c>
       <c r="B22" s="21">
-        <v>-0.05241953578085297</v>
+        <v>-0.05208890186740349</v>
       </c>
       <c r="C22" s="21">
-        <v>-0.0702217988069409</v>
+        <v>-0.06989785951258132</v>
       </c>
       <c r="D22" s="21">
-        <v>-0.08677804894618817</v>
+        <v>-0.08646031375945355</v>
       </c>
       <c r="E22" s="21">
-        <v>-0.1022325386301319</v>
+        <v>-0.10192056700168922</v>
       </c>
       <c r="F22" s="21">
-        <v>-0.11670682786380988</v>
+        <v>-0.11640024672750965</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2426,19 +2426,19 @@
         <v>104</v>
       </c>
       <c r="B23" s="21">
-        <v>-0.019335546899028114</v>
+        <v>-0.019072544563595355</v>
       </c>
       <c r="C23" s="21">
-        <v>-0.033522126621732574</v>
+        <v>-0.03326352265418744</v>
       </c>
       <c r="D23" s="21">
-        <v>-0.04676223108446978</v>
+        <v>-0.046507706161898595</v>
       </c>
       <c r="E23" s="21">
-        <v>-0.05916297392714407</v>
+        <v>-0.058912240110363154</v>
       </c>
       <c r="F23" s="21">
-        <v>-0.07081484079775355</v>
+        <v>-0.07056765695414785</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2446,19 +2446,19 @@
         <v>105</v>
       </c>
       <c r="B24" s="21">
-        <v>0.0010275990184110831</v>
+        <v>0.0012476074622711675</v>
       </c>
       <c r="C24" s="21">
-        <v>-0.010850842946301538</v>
+        <v>-0.010634117922615689</v>
       </c>
       <c r="D24" s="21">
-        <v>-0.02195675634252925</v>
+        <v>-0.021743072623183708</v>
       </c>
       <c r="E24" s="21">
-        <v>-0.03237670196213072</v>
+        <v>-0.03216584116413574</v>
       </c>
       <c r="F24" s="21">
-        <v>-0.04218386433190968</v>
+        <v>-0.041975645122366186</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2466,7 +2466,7 @@
         <v>106</v>
       </c>
       <c r="B25" s="21">
-        <v>-0.9214486787447773</v>
+        <v>-0.9194407911920734</v>
       </c>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
@@ -2478,10 +2478,10 @@
         <v>107</v>
       </c>
       <c r="B26" s="21">
-        <v>-0.594709807898429</v>
+        <v>-0.5921560265821006</v>
       </c>
       <c r="C26" s="21">
-        <v>-0.7631677139499173</v>
+        <v>-0.7592049811061883</v>
       </c>
       <c r="D26" s="25"/>
       <c r="E26" s="25"/>
@@ -2492,13 +2492,13 @@
         <v>108</v>
       </c>
       <c r="B27" s="21">
-        <v>-0.36799938996153103</v>
+        <v>-0.3661673160429264</v>
       </c>
       <c r="C27" s="21">
-        <v>-0.48317026009756003</v>
+        <v>-0.48068257686416105</v>
       </c>
       <c r="D27" s="21">
-        <v>-0.655732551528768</v>
+        <v>-0.6509032329555042</v>
       </c>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
@@ -2508,16 +2508,16 @@
         <v>109</v>
       </c>
       <c r="B28" s="21">
-        <v>-0.2331965698520404</v>
+        <v>-0.23189262774800862</v>
       </c>
       <c r="C28" s="21">
-        <v>-0.31241904292204625</v>
+        <v>-0.310780456085379</v>
       </c>
       <c r="D28" s="21">
-        <v>-0.4126986171541183</v>
+        <v>-0.41035514291603936</v>
       </c>
       <c r="E28" s="21">
-        <v>-0.5754666379315434</v>
+        <v>-0.5704172164294594</v>
       </c>
       <c r="F28" s="25"/>
     </row>
@@ -2526,19 +2526,19 @@
         <v>110</v>
       </c>
       <c r="B29" s="21">
-        <v>-0.149443859006734</v>
+        <v>-0.148475483141817</v>
       </c>
       <c r="C29" s="21">
-        <v>-0.2069096621857026</v>
+        <v>-0.20575281403470455</v>
       </c>
       <c r="D29" s="21">
-        <v>-0.2741712056398171</v>
+        <v>-0.2726929611950131</v>
       </c>
       <c r="E29" s="21">
-        <v>-0.36114706150567455</v>
+        <v>-0.3589906716660225</v>
       </c>
       <c r="F29" s="21">
-        <v>-0.5050197111863173</v>
+        <v>-0.5003626100852552</v>
       </c>
     </row>
   </sheetData>
